--- a/Assets/Tables/player.xlsx
+++ b/Assets/Tables/player.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\Doom\Assets\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F9F3B9-ECC1-4C8C-AA12-2EC965BAE565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2819EAD5-6275-43F3-9655-1A0FCE86F9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33315" yWindow="2010" windowWidth="27090" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="player" sheetId="2" r:id="rId1"/>
@@ -59,9 +59,6 @@
     <t>path</t>
   </si>
   <si>
-    <t>arrivals</t>
-  </si>
-  <si>
     <t>maa_1</t>
   </si>
   <si>
@@ -82,6 +79,10 @@
   </si>
   <si>
     <t>战士</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>scopes</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -485,12 +486,12 @@
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -500,12 +501,12 @@
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>5</v>
@@ -522,13 +523,13 @@
         <v>400000201</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>9</v>
       </c>
       <c r="E4" s="4">
         <v>100</v>

--- a/Assets/Tables/player.xlsx
+++ b/Assets/Tables/player.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\Doom\Assets\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2819EAD5-6275-43F3-9655-1A0FCE86F9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C1B19F-94C4-4EEF-8C8E-6598817FE530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33315" yWindow="2010" windowWidth="27090" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="2970" windowWidth="27090" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="player" sheetId="2" r:id="rId1"/>
@@ -41,9 +41,6 @@
     <t>name</t>
   </si>
   <si>
-    <t>arrival_asset_path</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -83,6 +80,10 @@
   </si>
   <si>
     <t>scopes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>fly_asset_path</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -482,40 +483,40 @@
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>4</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -523,13 +524,13 @@
         <v>400000201</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>14</v>
-      </c>
       <c r="D4" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="4">
         <v>100</v>
